--- a/reports/Debug-purgatory-20260104/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/Month to Date (Actual)_Visits.xlsx
@@ -437,7 +437,7 @@
         <v>46023</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -451,7 +451,7 @@
         <v>46024</v>
       </c>
       <c r="C3" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,10 +462,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,10 +476,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,10 +490,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C6" s="2">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C7" s="2">
-        <v>1100</v>
+        <v>1456</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -518,10 +518,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C8" s="2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,13 +532,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C9" s="2">
-        <v>1552</v>
+        <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C11" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -577,7 +577,7 @@
         <v>46026</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -605,10 +605,10 @@
         <v>46023</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C15" s="2">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <v>1445</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C18" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -675,7 +675,7 @@
         <v>46023</v>
       </c>
       <c r="C19" s="2">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -689,7 +689,7 @@
         <v>46024</v>
       </c>
       <c r="C20" s="2">
-        <v>1445</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,7 +700,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C22" s="2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -728,10 +728,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C24" s="2">
-        <v>8</v>
+        <v>406</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C25" s="2">
-        <v>1456</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -773,7 +773,7 @@
         <v>46025</v>
       </c>
       <c r="C26" s="2">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C27" s="2">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>528</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>936</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C30" s="2">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,13 +840,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C31" s="2">
-        <v>528</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C32" s="2">
-        <v>936</v>
+        <v>34</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C33" s="2">
-        <v>89</v>
+        <v>311</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C34" s="2">
-        <v>1</v>
+        <v>969</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -896,10 +896,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C35" s="2">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C36" s="2">
-        <v>311</v>
+        <v>14</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C37" s="2">
-        <v>969</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C39" s="2">
-        <v>608</v>
+        <v>310</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C41" s="2">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C42" s="2">
-        <v>1469</v>
+        <v>608</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C43" s="2">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C44" s="2">
-        <v>906</v>
+        <v>110</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>1469</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C47" s="2">
-        <v>56</v>
+        <v>906</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C50" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C51" s="2">
-        <v>89</v>
+        <v>1552</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C52" s="2">
-        <v>406</v>
+        <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C53" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C54" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1179,7 +1179,7 @@
         <v>46026</v>
       </c>
       <c r="C55" s="2">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
